--- a/stories/arbres/ATOM-REL.CON.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est au parc avec papa. Papa s'assoit sur le banc. Nora joue près du bac à sable. Le sable est frais sous les doigts. Sami court vers le bac. Sami bouscule Nora. Nora sent un choc. Son cœur bat vite. Nora dit : stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Nora marche vers le banc. Papa est son parent au parc. Nora rejoint son parent au parc. Elle dit : Sami m'a bousculée. Papa l'écoute. Papa dit : tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.</t>
+          <t>Nora est au parc avec papa. Papa s'assoit sur le banc. Nora joue près du bac à sable. Le sable est frais sous les doigts. Sami court vers le bac. Sami bouscule Nora. Nora sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Nora marche vers le banc. Papa est son parent au parc. Nora rejoint son parent au parc. Sami m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est au parc avec papa. Papa s'assoit sur le banc. Nora joue près du bac à sable. Le sable est frais sous les doigts. Sami court vers le bac. Sami bouscule Nora. Nora sent un choc. Son cœur bat vite.
+enfant-f|Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa.
+narrateur|Nora marche vers le banc. Papa est son parent au parc. Nora rejoint son parent au parc.
+narrateur|Sami m'a bousculée. Papa l'écoute.
+papa|Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main.
+narrateur|Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Nora. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nora boit une gorgée d'eau. Papa garde sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Un camarade bouscule Nora. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,11 @@
           <t>narrateur|Nora a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1852,7 @@
           <t>narrateur|Nora boit une gorgée d'eau. Papa garde sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dire stop et rejoindre un adulte au parc</t>
+          <t>Le seau jaune de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, un seau jaune attend près du bac. Sarah veut le remplir. Nino arrive trop vite. Elle dit stop, s'éloigne, rejoint papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est au parc avec papa. Papa s'assoit sur le banc. Nora joue près du bac à sable. Le sable est frais sous les doigts. Sami court vers le bac. Sami bouscule Nora. Nora sent un choc. Son cœur bat vite. Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Nora marche vers le banc. Papa est son parent au parc. Nora rejoint son parent au parc. Sami m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.</t>
+          <t>La grille du parc est encore mouillée. Une petite flaque brille sur le chemin. Ça sent la terre et l'herbe coupée. Un pigeon picore près des trous d'eau. Le banc de bois a des gouttes. Papa pose le sac du goûter. Le pain sent encore le four du village. Viens, Sarah. Le parc est calme, après la pluie. Le seau jaune t'attend près du bac. En ce moment, Sarah s'accroupit. Le sable est frais sous ses doigts. Il est un peu collant, un peu froid. Le seau est jaune, papa. Oui. C'est ton seau. Tu mets le sable dedans ? Sarah prend le seau. Le plastique est lisse et un peu froid. Elle verse le sable tout doucement. Ça fait un bruit de pluie fine. Bravo. Tu travailles bien. Un papillon passe tout près du bac. Il est jaune, comme le seau. Il vole, papa. Oui. Il est tout léger. Nino arrive trop vite vers le bac. Sarah sent un choc à l'épaule. Son cœur bat très vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Sarah marche vers le banc. Papa est son parent au parc. Sarah rejoint son parent au parc. Nino m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Sarah. C'est du bon travail. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat encore. On souffle ensemble ? Sarah souffle doucement. Le banc sèche au soleil. Les oiseaux chantent tout près. Tu veux un peu d'eau ? Oui, papa. Sarah boit une gorgée. L'eau est fraîche. Tu restes près de moi. Je suis ton parent au parc. Le seau jaune attend près du bac. Sarah reste près de son parent au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nora est au parc avec papa. Papa s'assoit sur le banc. Nora joue près du bac à sable. Le sable est frais sous les doigts. Sami court vers le bac. Sami bouscule Nora. Nora sent un choc. Son cœur bat vite.
-enfant-f|Stop. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa.
-narrateur|Nora marche vers le banc. Papa est son parent au parc. Nora rejoint son parent au parc.
-narrateur|Sami m'a bousculée. Papa l'écoute.
-papa|Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main.
-narrateur|Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.</t>
+          <t>narrateur|La grille du parc est encore mouillée.
+narrateur|Une petite flaque brille sur le chemin.
+narrateur|Ça sent la terre et l'herbe coupée.
+narrateur|Un pigeon picore près des trous d'eau.
+narrateur|Le banc de bois a des gouttes.
+narrateur|Papa pose le sac du goûter.
+narrateur|Le pain sent encore le four du village.
+papa|Viens, Sarah.
+papa|Le parc est calme, après la pluie.
+papa|Le seau jaune t'attend près du bac.
+narrateur|En ce moment, Sarah s'accroupit.
+narrateur|Le sable est frais sous ses doigts.
+narrateur|Il est un peu collant, un peu froid.
+enfant-f|Le seau est jaune, papa.
+papa|Oui.
+papa|C'est ton seau.
+papa|Tu mets le sable dedans ?
+narrateur|Sarah prend le seau.
+narrateur|Le plastique est lisse et un peu froid.
+narrateur|Elle verse le sable tout doucement.
+narrateur|Ça fait un bruit de pluie fine.
+papa|Bravo.
+papa|Tu travailles bien.
+narrateur|Un papillon passe tout près du bac.
+narrateur|Il est jaune, comme le seau.
+enfant-f|Il vole, papa.
+papa|Oui.
+papa|Il est tout léger.
+narrateur|Nino arrive trop vite vers le bac.
+narrateur|Sarah sent un choc à l'épaule.
+narrateur|Son cœur bat très vite.
+enfant-f|Stop.
+narrateur|Elle fait un pas de côté.
+narrateur|Elle s'éloigne.
+narrateur|S'éloigner, c'est marcher vers papa.
+narrateur|Sarah marche vers le banc.
+narrateur|Papa est son parent au parc.
+narrateur|Sarah rejoint son parent au parc.
+enfant-f|Nino m'a bousculée.
+narrateur|Papa l'écoute.
+papa|Tu as dit stop.
+papa|Tu t'es éloignée.
+papa|Tu es venue vers moi.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+papa|Donne-moi ta main.
+narrateur|Papa lui tient la main.
+narrateur|La main de papa est tiède.
+enfant-f|Mon cœur bat encore.
+papa|On souffle ensemble ?
+narrateur|Sarah souffle doucement.
+narrateur|Le banc sèche au soleil.
+narrateur|Les oiseaux chantent tout près.
+papa|Tu veux un peu d'eau ?
+enfant-f|Oui, papa.
+narrateur|Sarah boit une gorgée.
+narrateur|L'eau est fraîche.
+papa|Tu restes près de moi.
+papa|Je suis ton parent au parc.
+narrateur|Le seau jaune attend près du bac.
+narrateur|Sarah reste près de son parent au parc.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Nora. Que fait-elle ?</t>
+          <t>Un camarade bouscule Sarah. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1572,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Nora. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Un camarade bouscule Sarah.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
+          <t>Sarah a dit stop. Elle s'est éloignée. Elle a rejoint son parent au parc. Tu es venue vers moi. Bravo. Tu as fini ta gorgée ? Presque, papa. Le seau peut attendre. Sarah pose la main sur le bois du banc. Le bois est encore un peu humide. Le pigeon picore plus loin. Je suis là, près de toi. Papa est son parent au parc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1744,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora a dit stop. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.</t>
+          <t>narrateur|Sarah a dit stop.
+narrateur|Elle s'est éloignée.
+narrateur|Elle a rejoint son parent au parc.
+papa|Tu es venue vers moi.
+papa|Bravo.
+papa|Tu as fini ta gorgée ?
+enfant-f|Presque, papa.
+papa|Le seau peut attendre.
+narrateur|Sarah pose la main sur le bois du banc.
+narrateur|Le bois est encore un peu humide.
+narrateur|Le pigeon picore plus loin.
+papa|Je suis là, près de toi.
+narrateur|Papa est son parent au parc.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1709,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nora boit une gorgée d'eau. Papa garde sa main.</t>
+          <t>Papa range la gourde dans le sac. Le pain sent encore le four. Tu veux un morceau ? Oui. Sarah croque le pain. Il est doux et un peu tiède. Donne-moi ta main encore. Papa garde sa main. On reste un peu sur le banc ? Oui, papa. La flaque devient toute petite. Le seau jaune brille au soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,10 +1928,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nora boit une gorgée d'eau. Papa garde sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range la gourde dans le sac.
+narrateur|Le pain sent encore le four.
+papa|Tu veux un morceau ?
+enfant-f|Oui.
+narrateur|Sarah croque le pain.
+narrateur|Il est doux et un peu tiède.
+papa|Donne-moi ta main encore.
+narrateur|Papa garde sa main.
+papa|On reste un peu sur le banc ?
+enfant-f|Oui, papa.
+narrateur|La flaque devient toute petite.
+narrateur|Le seau jaune brille au soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1877,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venue vers toi. Bravo, Sarah. Tu as fait du bon travail. Le seau jaune reste près du bac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,10 +2106,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|J'ai dit stop.
+enfant-f|Je suis venue vers toi.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Le seau jaune reste près du bac.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2039,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La grille du parc est encore mouillée. Une petite flaque brille sur le chemin. Ça sent la terre et l'herbe coupée. Un pigeon picore près des trous d'eau. Le banc de bois a des gouttes. Papa pose le sac du goûter. Le pain sent encore le four du village. Viens, Sarah. Le parc est calme, après la pluie. Le seau jaune t'attend près du bac. En ce moment, Sarah s'accroupit. Le sable est frais sous ses doigts. Il est un peu collant, un peu froid. Le seau est jaune, papa. Oui. C'est ton seau. Tu mets le sable dedans ? Sarah prend le seau. Le plastique est lisse et un peu froid. Elle verse le sable tout doucement. Ça fait un bruit de pluie fine. Bravo. Tu travailles bien. Un papillon passe tout près du bac. Il est jaune, comme le seau. Il vole, papa. Oui. Il est tout léger. Nino arrive trop vite vers le bac. Sarah sent un choc à l'épaule. Son cœur bat très vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Sarah marche vers le banc. Papa est son parent au parc. Sarah rejoint son parent au parc. Nino m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Sarah. C'est du bon travail. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat encore. On souffle ensemble ? Sarah souffle doucement. Le banc sèche au soleil. Les oiseaux chantent tout près. Tu veux un peu d'eau ? Oui, papa. Sarah boit une gorgée. L'eau est fraîche. Tu restes près de moi. Je suis ton parent au parc. Le seau jaune attend près du bac. Sarah reste près de son parent au parc.</t>
+          <t>La grille du parc est encore mouillée. Une petite flaque brille sur le chemin. Ça sent la terre et l'herbe coupée. Un pigeon picore près des trous d'eau. Le banc de bois a des gouttes. Papa pose le sac du goûter. Le pain sent encore le four du village. Viens, Sarah. Le parc est calme, après la pluie. Le seau jaune t'attend près du bac. En ce moment, Sarah s'accroupit. Le sable est frais sous ses doigts. Il est un peu collant, un peu froid. Le seau est jaune, papa. Oui. C'est ton seau. Tu mets le sable dedans ? Sarah prend le seau. Le plastique est lisse et un peu froid. Elle verse le sable tout doucement. Ça fait un bruit de pluie fine. Bravo. Tu travailles bien. Un papillon passe tout près du bac. Il est jaune, comme le seau. Il vole, papa. Oui. Il est tout léger. Nino arrive trop vite vers le bac. Sarah sent un choc à l'épaule. Son cœur bat très vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Sarah marche vers le banc. Papa est son parent au parc. Sarah rejoint son parent au parc. Nino m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Sarah. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat encore. On souffle ensemble ? Sarah souffle doucement. Le banc sèche au soleil. Les oiseaux chantent tout près. Tu veux un peu d'eau ? Oui, papa. Sarah boit une gorgée. L'eau est fraîche. Tu restes près de moi. Je suis ton parent au parc. Le seau jaune attend près du bac. Sarah reste près de son parent au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora est au parc avec papa. Papa s'assoit sur le banc. Nora joue près du bac à sable. Le sable est frais sous les doigts. Sami court vers le bac. Sami bouscule Nora. Nora sent un choc. Son cœur bat vite. Nora dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle fait un pas de côté. Elle doit s'éloigner. S'éloigner, c'est marcher vers papa. Nora marche vers le banc. Papa est son parent au parc. Nora rejoint son parent au parc. Elle dit : Sami m'a bousculée. Papa l'écoute. Papa dit : tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Papa lui tient la main. Nora souffle doucement. Le banc est calme. Les oiseaux chantent. Papa reste avec elle. Nora reste près de son parent au parc.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La grille du parc est encore mouillée. Une petite flaque brille sur le chemin. Ça sent la terre et l'herbe coupée. Un pigeon picore près des trous d'eau. Le banc de bois a des gouttes. Papa pose le sac du goûter. Le pain sent encore le four du village. Viens, Sarah. Le parc est calme, après la pluie. Le seau jaune t'attend près du bac. En ce moment, Sarah s'accroupit. Le sable est frais sous ses doigts. Il est un peu collant, un peu froid. Le seau est jaune, papa. Oui. C'est ton seau. Tu mets le sable dedans ? Sarah prend le seau. Le plastique est lisse et un peu froid. Elle verse le sable tout doucement. Ça fait un bruit de pluie fine. Bravo. Tu travailles bien. Un papillon passe tout près du bac. Il est jaune, comme le seau. Il vole, papa. Oui. Il est tout léger. Nino arrive trop vite vers le bac. Sarah sent un choc à l'épaule. Son cœur bat très vite. Stop. Elle fait un pas de côté. Elle s'éloigne. S'éloigner, c'est marcher vers papa. Sarah marche vers le banc. Papa est son parent au parc. Sarah rejoint son parent au parc. Nino m'a bousculée. Papa l'écoute. Tu as dit stop. Tu t'es éloignée. Tu es venue vers moi. Bravo, Sarah. Donne-moi ta main. Papa lui tient la main. La main de papa est tiède. Mon cœur bat encore. On souffle ensemble ? Sarah souffle doucement. Le banc sèche au soleil. Les oiseaux chantent tout près. Tu veux un peu d'eau ? Oui, papa. Sarah boit une gorgée. L'eau est fraîche. Tu restes près de moi. Je suis ton parent au parc. Le seau jaune attend près du bac. Sarah reste près de son parent au parc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1368,7 +1368,6 @@
 papa|Tu t'es éloignée.
 papa|Tu es venue vers moi.
 papa|Bravo, Sarah.
-papa|C'est du bon travail.
 papa|Donne-moi ta main.
 narrateur|Papa lui tient la main.
 narrateur|La main de papa est tiède.
@@ -1421,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Un camarade bouscule Nora. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Sarah. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1605,7 +1604,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle a su s'éloigner. Elle a rejoint son parent au parc. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a dit stop. Elle s'est éloignée. Elle a rejoint son parent au parc. Tu es venue vers moi. Bravo. Tu as fini ta gorgée ? Presque, papa. Le seau peut attendre. Sarah pose la main sur le bois du banc. Le bois est encore un peu humide. Le pigeon picore plus loin. Je suis là, près de toi. Papa est son parent au parc.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1793,7 +1792,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora boit une gorgée d'eau. Papa garde sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range la gourde dans le sac. Le pain sent encore le four. Tu veux un morceau ? Oui. Sarah croque le pain. Il est doux et un peu tiède. Donne-moi ta main encore. Papa garde sa main. On reste un peu sur le banc ? Oui, papa. La flaque devient toute petite. Le seau jaune brille au soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1966,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis venue vers toi. Bravo, Sarah. Tu as fait du bon travail. Le seau jaune reste près du bac. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venue vers toi. Bravo, Sarah. Le seau jaune reste près du bac.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis venue vers toi. Bravo, Sarah. Le seau jaune reste près du bac.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,9 +2108,7 @@
           <t>enfant-f|J'ai dit stop.
 enfant-f|Je suis venue vers toi.
 papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
-narrateur|Le seau jaune reste près du bac.
-narrateur|L'histoire est finie.</t>
+narrateur|Le seau jaune reste près du bac.</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2174,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc après la pluie, bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nora, Sami, papa</t>
+          <t>Sarah, Nino, papa</t>
         </is>
       </c>
     </row>
